--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbCalendarInfo001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbCalendarInfo001.xlsx
@@ -406,11 +406,11 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576">
       <formula1>"01 中国法定节假日,02 美国法定节假日,03 银行间,04 上交所,05 深交所,06 商业银行柜台市场,07 其他,08 香港节假日,09 澳大利亚节假日,10 欧元区节假日,11 美元节假日,12 伦敦节假日"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576">
-      <formula1>"0 否,1 是"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576">
+      <formula1>"0 工作日,1 节假日"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
